--- a/public/documentation/assessment/BI/Distribution/Tableau/Cross Sell Dashboard/Cross Sell Dashboard_Assessment.xlsx
+++ b/public/documentation/assessment/BI/Distribution/Tableau/Cross Sell Dashboard/Cross Sell Dashboard_Assessment.xlsx
@@ -3,11 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Overview &amp; Metadata" sheetId="1" r:id="rId1"/>
-    <sheet name="KPIs &amp; Business Metrics" sheetId="2" r:id="rId2"/>
-    <sheet name="Data Sources &amp; Tables" sheetId="3" r:id="rId3"/>
-    <sheet name="Target Outputs" sheetId="4" r:id="rId4"/>
-    <sheet name="Complexity &amp; Risk Score" sheetId="5" r:id="rId5"/>
+    <sheet name="Asset Overview" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -405,7 +401,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Attribute</v>
+        <v>Property</v>
       </c>
       <c r="B1" t="str">
         <v>Value</v>
@@ -421,15 +417,15 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Domain</v>
+        <v>Asset ID</v>
       </c>
       <c r="B3" t="str">
-        <v>Business Intelligence (BI)</v>
+        <v>d2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Technology Platform</v>
+        <v>Technology</v>
       </c>
       <c r="B4" t="str">
         <v>Tableau</v>
@@ -445,50 +441,50 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Asset Owner</v>
+        <v>Asset Type</v>
       </c>
       <c r="B6" t="str">
-        <v>Amanda Foster</v>
+        <v>Dashboard</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Connected Sources Count</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
+        <v>Owner</v>
+      </c>
+      <c r="B7" t="str">
+        <v>EXLDistribution</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Data Target Feeds Count</v>
+        <v>KPI Count</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Tracked KPIs Count</v>
+        <v>Calculated Fields</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Business Description</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Policy cross-selling opportunities across commercial, property, and casualty lines.</v>
+        <v>Worksheets / Pages</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Assessment Health Status</v>
+        <v>Description</v>
       </c>
       <c r="B11" t="str">
-        <v>Validated</v>
+        <v>Policy cross-selling opportunities across commercial, property, and casualty lines.</v>
       </c>
     </row>
   </sheetData>
@@ -496,318 +492,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>KPI #</v>
-      </c>
-      <c r="B1" t="str">
-        <v>KPI Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Business Importance</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Update Frequency</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Calculation Type</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Cross-Sell Ratio</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Critical</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Aggregated Fact Metric</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Multi-policy Discount Impact</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Critical</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Aggregated Fact Metric</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Bundled Renewal Rate</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Critical</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Aggregated Fact Metric</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Customer Lifetime Value</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Operational</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Aggregated Fact Metric</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Agent Cross-sell Commission</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Operational</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Aggregated Fact Metric</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Line of Business Penetration</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Operational</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Daily</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Aggregated Fact Metric</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Source #</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Table / Source Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Source System</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Format</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Refresh Schedule</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>policy_customer_mapping_fact</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Enterprise Insurance Data Lake / DW</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Relational View / Fact Table</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Nightly at 01:00 AM</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>product_crosssell_matrix</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Enterprise Insurance Data Lake / DW</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Relational View / Fact Table</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Nightly at 01:00 AM</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>agent_performance_dim</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Enterprise Insurance Data Lake / DW</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Relational View / Fact Table</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Nightly at 01:00 AM</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Target #</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Output Target</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Consumer System</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Format</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>cross_sell_analytics.hyper</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Executive &amp; Operational Insurance Users</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Tableau Hyper Extract</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Metric</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Score</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Evaluation</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Data Model Complexity</v>
-      </c>
-      <c r="B2" t="str">
-        <v>7.8 / 10</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Moderate multi-table snowflake schema</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Calculation Logic Complexity</v>
-      </c>
-      <c r="B3" t="str">
-        <v>6.5 / 10</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Standard aggregations with several LOD expressions</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Security &amp; Access Governance</v>
-      </c>
-      <c r="B4" t="str">
-        <v>8.2 / 10</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Row-level security based on adjuster region</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Overall Modernization Effort</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Straightforward conversion to modern self-service</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
-  </ignoredErrors>
-</worksheet>
 </file>